--- a/books.xlsx
+++ b/books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krishnendu Bir\Desktop\medicoupne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632C8C1A-ED5C-440B-BC0B-A2BE851C6A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D47843E-2B59-468F-9BD4-A5D7897C252D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3B2F283F-4E6A-4BE6-927C-24D78D64D2AD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>Year</t>
   </si>
@@ -51,18 +51,12 @@
     <t>MBBS 2nd Year</t>
   </si>
   <si>
-    <t>KD Tripathi</t>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
     <t>Human Anatomy (Vol 1-3)</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/71R2c3bJ5lL.SY445_SX342.jpg</t>
-  </si>
-  <si>
     <t>BD Chaurasia</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>Medical Physiology</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/81xU2p69h3L.SY445_SX342.jpg</t>
-  </si>
-  <si>
     <t>Comprehensive physiological processes</t>
   </si>
   <si>
@@ -87,9 +78,6 @@
     <t>Biochemistry</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/81B-74Vj4xL.SY445_SX342.jpg</t>
-  </si>
-  <si>
     <t>U. Satyanarayana</t>
   </si>
   <si>
@@ -99,24 +87,9 @@
     <t>https://www.amazon.in/dp/8131248852</t>
   </si>
   <si>
-    <t>Medical Pharmacology</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81t-sC+N14L.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>Standard Indian pharmacology text</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/9352704561</t>
-  </si>
-  <si>
     <t>Textbook of Pathology</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/71X8k+E3eTL.SY445_SX342.jpg</t>
-  </si>
-  <si>
     <t>Harsh Mohan</t>
   </si>
   <si>
@@ -129,9 +102,6 @@
     <t>Pathologic Basis of Disease</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/81q2X9p2w6L.SY445_SX342.jpg</t>
-  </si>
-  <si>
     <t>Robbins &amp; Cotran</t>
   </si>
   <si>
@@ -144,9 +114,6 @@
     <t>Textbook of Microbiology</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/71F2-Qk7bLL.SY445_SX342.jpg</t>
-  </si>
-  <si>
     <t>Ananthanarayan &amp; Paniker</t>
   </si>
   <si>
@@ -156,115 +123,22 @@
     <t>https://www.amazon.in/dp/9389587423</t>
   </si>
   <si>
-    <t>MBBS 3rd Year</t>
-  </si>
-  <si>
-    <t>Preventive and Social Medicine</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81G3-G7dD4L.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>K. Park</t>
-  </si>
-  <si>
-    <t>Gold standard for community medicine</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/9382219159</t>
-  </si>
-  <si>
-    <t>Diseases of Ear, Nose and Throat</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/71Q8tJ6v01L.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>PL Dhingra</t>
-  </si>
-  <si>
-    <t>Essential textbook for ENT</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/8131248844</t>
-  </si>
-  <si>
-    <t>Comprehensive Ophthalmology</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81Z-2q7E-FL.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>AK Khurana</t>
-  </si>
-  <si>
-    <t>Standard eye disease reference</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/9389587814</t>
-  </si>
-  <si>
-    <t>MBBS Final Year</t>
-  </si>
-  <si>
-    <t>Principles and Practice of Medicine</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81k3yWv6-4L.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>Davidson</t>
-  </si>
-  <si>
-    <t>Core text for internal medicine</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/0702070289</t>
-  </si>
-  <si>
-    <t>Short Practice of Surgery</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81jZ9jY8LJL.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>Bailey &amp; Love</t>
-  </si>
-  <si>
-    <t>Essential surgical techniques guide</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/1498751532</t>
-  </si>
-  <si>
-    <t>Textbook of Obstetrics</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/71s6rO5S7rL.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>DC Dutta</t>
-  </si>
-  <si>
-    <t>Extensive guide to obstetrics</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/9389587571</t>
-  </si>
-  <si>
-    <t>Essential Pediatrics</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81L-8v7wLqL.SY445_SX342.jpg</t>
-  </si>
-  <si>
-    <t>OP Ghai</t>
-  </si>
-  <si>
-    <t>Widely recommended pediatrics text</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/dp/9389188049</t>
+    <t>https://m.media-amazon.com/images/I/71OeY5+YkxL._SY522_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/616nrzJUJhL._AC_UY327_FMwebp_QL65_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71tUp8W4c3L._AC_UY327_FMwebp_QL65_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71uaNIlJCUL._AC_UY327_FMwebp_QL65_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81oiCb8RqvL._AC_UY327_FMwebp_QL65_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61lvFW6x3RL._AC_UY327_FMwebp_QL65_.jpg</t>
   </si>
 </sst>
 </file>
@@ -663,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9387BB90-600A-4AE9-92B2-0A88DC4F4A48}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
@@ -682,7 +556,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -696,19 +570,19 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -716,19 +590,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -736,19 +610,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -756,19 +630,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -776,231 +650,111 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="84.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/71R2c3bJ5lL._SY445_SX342_.jpg" xr:uid="{B0A24185-F90B-4E79-A4DE-6673D1A3A702}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B0A24185-F90B-4E79-A4DE-6673D1A3A702}"/>
     <hyperlink ref="F2" r:id="rId2" display="https://www.google.com/search?q=https://www.amazon.in/dp/9389809426" xr:uid="{936CAB66-8046-44D7-BD46-3DE1235773C5}"/>
-    <hyperlink ref="C3" r:id="rId3" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81xU2p69h3L._SY445_SX342_.jpg" xr:uid="{524BF21C-658C-41D6-AE5E-4511B7926E64}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{524BF21C-658C-41D6-AE5E-4511B7926E64}"/>
     <hyperlink ref="F3" r:id="rId4" display="https://www.google.com/search?q=https://www.amazon.in/dp/813125979X" xr:uid="{3D0D0552-78B9-467B-BA34-4516E25BAF8D}"/>
-    <hyperlink ref="C4" r:id="rId5" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81B-74Vj4xL._SY445_SX342_.jpg" xr:uid="{E6FBA6C1-91E8-4544-AF98-7B82B21F0B37}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{E6FBA6C1-91E8-4544-AF98-7B82B21F0B37}"/>
     <hyperlink ref="F4" r:id="rId6" display="https://www.google.com/search?q=https://www.amazon.in/dp/8131248852" xr:uid="{DDCDFA72-AB93-449E-97FC-FAA6C18F01CD}"/>
-    <hyperlink ref="C5" r:id="rId7" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81t-sC%2BN14L._SY445_SX342_.jpg" xr:uid="{073C337B-257B-4260-9DDB-E142C2C02B6E}"/>
-    <hyperlink ref="F5" r:id="rId8" display="https://www.google.com/search?q=https://www.amazon.in/dp/9352704561" xr:uid="{855AB20C-ACFE-46B6-8FDE-F4862BD84524}"/>
-    <hyperlink ref="C6" r:id="rId9" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/71X8k%2BE3eTL._SY445_SX342_.jpg" xr:uid="{60F14D07-CA62-4DC1-B119-09F919D9912B}"/>
-    <hyperlink ref="F6" r:id="rId10" display="https://www.google.com/search?q=https://www.amazon.in/dp/9352704383" xr:uid="{20541782-90C3-48A1-AD8D-FC2C355B3E0E}"/>
-    <hyperlink ref="C7" r:id="rId11" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81q2X9p2w6L._SY445_SX342_.jpg" xr:uid="{8AA72722-39F6-4019-9BCC-F5E6D68F966D}"/>
-    <hyperlink ref="F7" r:id="rId12" display="https://www.google.com/search?q=https://www.amazon.in/dp/8131240312" xr:uid="{43FCE1D9-40AC-42EE-9616-AA004D3B886F}"/>
-    <hyperlink ref="C8" r:id="rId13" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/71F2-Qk7bLL._SY445_SX342_.jpg" xr:uid="{349EB9FF-0F51-43EA-A9B9-AFDD40A74B32}"/>
-    <hyperlink ref="F8" r:id="rId14" display="https://www.google.com/search?q=https://www.amazon.in/dp/9389587423" xr:uid="{C6894C5B-6041-450D-8F12-4E144F7862A3}"/>
-    <hyperlink ref="C9" r:id="rId15" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81G3-G7dD4L._SY445_SX342_.jpg" xr:uid="{9AB57A85-FEB2-40B7-BF60-375DBECAA550}"/>
-    <hyperlink ref="F9" r:id="rId16" display="https://www.google.com/search?q=https://www.amazon.in/dp/9382219159" xr:uid="{D8C7F17D-FCA2-4492-923A-28D539AF87EA}"/>
-    <hyperlink ref="C10" r:id="rId17" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/71Q8tJ6v01L._SY445_SX342_.jpg" xr:uid="{50CC0564-CDE6-4AF5-98F3-FE50B8031E1F}"/>
-    <hyperlink ref="F10" r:id="rId18" display="https://www.google.com/search?q=https://www.amazon.in/dp/8131248844" xr:uid="{3A2333F8-CA75-4D0E-B9A4-1C55A2181AB7}"/>
-    <hyperlink ref="C11" r:id="rId19" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81Z-2q7E-FL._SY445_SX342_.jpg" xr:uid="{F2B1D874-ED9A-49AB-9A91-205961EA067A}"/>
-    <hyperlink ref="F11" r:id="rId20" display="https://www.google.com/search?q=https://www.amazon.in/dp/9389587814" xr:uid="{4D099F39-7674-40DD-9E75-F28B52F31A55}"/>
-    <hyperlink ref="C12" r:id="rId21" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81k3yWv6-4L._SY445_SX342_.jpg" xr:uid="{8755EEEF-8914-4BD7-8AA4-396447E476E9}"/>
-    <hyperlink ref="F12" r:id="rId22" display="https://www.google.com/search?q=https://www.amazon.in/dp/0702070289" xr:uid="{0A14E013-77C0-4137-A8CD-8802B159FD73}"/>
-    <hyperlink ref="C13" r:id="rId23" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81jZ9jY8LJL._SY445_SX342_.jpg" xr:uid="{8003CD75-F39E-426A-A6EE-1A281E7DF2A8}"/>
-    <hyperlink ref="F13" r:id="rId24" display="https://www.google.com/search?q=https://www.amazon.in/dp/1498751532" xr:uid="{53EF38C4-C710-4C36-A8E3-3B0F94A72C28}"/>
-    <hyperlink ref="C14" r:id="rId25" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/71s6rO5S7rL._SY445_SX342_.jpg" xr:uid="{E46FD9A3-17AA-445F-AE66-8D8928C23FB2}"/>
-    <hyperlink ref="F14" r:id="rId26" display="https://www.google.com/search?q=https://www.amazon.in/dp/9389587571" xr:uid="{D9BD740C-1231-4A1A-B25C-D1255DD4227A}"/>
-    <hyperlink ref="C15" r:id="rId27" display="https://www.google.com/search?q=https://m.media-amazon.com/images/I/81L-8v7wLqL._SY445_SX342_.jpg" xr:uid="{A4B671F2-8F64-4AC7-A301-27016217FA18}"/>
-    <hyperlink ref="F15" r:id="rId28" display="https://www.google.com/search?q=https://www.amazon.in/dp/9389188049" xr:uid="{773B48AC-4CE5-4643-9F50-E57FBADF7704}"/>
+    <hyperlink ref="C5" r:id="rId7" xr:uid="{60F14D07-CA62-4DC1-B119-09F919D9912B}"/>
+    <hyperlink ref="F5" r:id="rId8" display="https://www.google.com/search?q=https://www.amazon.in/dp/9352704383" xr:uid="{20541782-90C3-48A1-AD8D-FC2C355B3E0E}"/>
+    <hyperlink ref="C6" r:id="rId9" xr:uid="{8AA72722-39F6-4019-9BCC-F5E6D68F966D}"/>
+    <hyperlink ref="F6" r:id="rId10" display="https://www.google.com/search?q=https://www.amazon.in/dp/8131240312" xr:uid="{43FCE1D9-40AC-42EE-9616-AA004D3B886F}"/>
+    <hyperlink ref="C7" r:id="rId11" xr:uid="{349EB9FF-0F51-43EA-A9B9-AFDD40A74B32}"/>
+    <hyperlink ref="F7" r:id="rId12" display="https://www.google.com/search?q=https://www.amazon.in/dp/9389587423" xr:uid="{C6894C5B-6041-450D-8F12-4E144F7862A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
